--- a/example_run/sourced_bom.xlsx
+++ b/example_run/sourced_bom.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Portal URL</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Purchase URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -566,6 +571,7 @@
           <t>quotes@mcmaster-example.com</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -634,6 +640,7 @@
           <t>sales@fastenco-example.com</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -702,6 +709,7 @@
           <t>sales@andymark-example.com</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -752,13 +760,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>UNEXPLORED_SOURCE</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>NEEDS_QUALIFICATION</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://www.electroconn-example.com/products/TB-100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -832,6 +849,7 @@
           <t>https://portal.linearmotion-example.com/rfq</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -882,13 +900,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UNEXPLORED_SOURCE</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>NEEDS_QUALIFICATION</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://www.meantech-example.com/shop/PSU-24-5A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -931,6 +958,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1084,7 +1112,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'ElectroConn' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'ElectroConn' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1122,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'MeanTech' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'MeanTech' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
